--- a/PUEYRREDON 1494/Septiembre/PUEYRREDON Septiembre.xlsx
+++ b/PUEYRREDON 1494/Septiembre/PUEYRREDON Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PUEYRREDON 1494\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F956CA-2567-4278-84EA-16F3B75B89A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48439119-F01D-4588-AE38-E3A92AA95D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$114</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$113</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="164">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -471,33 +471,6 @@
     <t>Lourdes</t>
   </si>
   <si>
-    <t>Transf 19/08</t>
-  </si>
-  <si>
-    <t>Efect 02/08</t>
-  </si>
-  <si>
-    <t>PMC 12/08</t>
-  </si>
-  <si>
-    <t>PMC 04/08</t>
-  </si>
-  <si>
-    <t>Transf 04/08</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
-  </si>
-  <si>
-    <t>Servisur - cambio de lamparas</t>
-  </si>
-  <si>
-    <t>Debito 26/08</t>
-  </si>
-  <si>
     <t>Deposito ya identificado del mes anterior</t>
   </si>
   <si>
@@ -516,10 +489,34 @@
     <t>Mantenimiento Ascensores - Mes de SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Reparacion de bomba tango 20 inteligente</t>
-  </si>
-  <si>
     <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Reliquidacion de deuda de unidades funcionales - Mateo Quotteri</t>
+  </si>
+  <si>
+    <t>Debito 12/09</t>
+  </si>
+  <si>
+    <t>PMC 12/09</t>
+  </si>
+  <si>
+    <t>Debito 30/09</t>
+  </si>
+  <si>
+    <t>No se debito</t>
+  </si>
+  <si>
+    <t>Transf 30/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
+  </si>
+  <si>
+    <t>Yamil Martinez</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1199,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1369,9 +1366,6 @@
     <xf numFmtId="8" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1407,35 +1401,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1450,26 +1430,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1487,8 +1467,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1844,111 +1835,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M118"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="141"/>
-      <c r="B1" s="142"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="144"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="145"/>
-      <c r="B2" s="137" t="s">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="144"/>
+      <c r="B2" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="146"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="145"/>
-      <c r="B3" s="137" t="s">
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="145"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="144"/>
+      <c r="B3" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="146"/>
-    </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="145"/>
-      <c r="B4" s="138" t="s">
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="145"/>
+    </row>
+    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="144"/>
+      <c r="B4" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="139" t="s">
+      <c r="C4" s="136"/>
+      <c r="D4" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="146"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="145" t="s">
+      <c r="E4" s="145"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="144" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="147"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="145" t="s">
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="146"/>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="136" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="136"/>
-      <c r="D6" s="137" t="s">
+      <c r="B6" s="135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="147"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="148" t="s">
+      <c r="E6" s="146"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="149"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="150"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="155" t="s">
-        <v>158</v>
+      <c r="B7" s="148"/>
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="149"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="168" t="s">
+        <v>149</v>
       </c>
       <c r="C9" s="156"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="156"/>
       <c r="C10" s="156"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="156"/>
       <c r="C11" s="156"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="133">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="132">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="159" t="s">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="169" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="156"/>
@@ -1956,33 +1947,33 @@
       <c r="D14" s="156"/>
       <c r="E14" s="156"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="156"/>
       <c r="B15" s="156"/>
       <c r="C15" s="156"/>
       <c r="D15" s="156"/>
       <c r="E15" s="156"/>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="156"/>
       <c r="B16" s="156"/>
       <c r="C16" s="156"/>
       <c r="D16" s="156"/>
       <c r="E16" s="156"/>
     </row>
-    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="156"/>
       <c r="B17" s="156"/>
       <c r="C17" s="156"/>
       <c r="D17" s="156"/>
       <c r="E17" s="156"/>
     </row>
-    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>10</v>
       </c>
@@ -1991,7 +1982,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>11</v>
       </c>
@@ -2000,41 +1991,41 @@
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
     </row>
-    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="120">
-        <v>798601.4</v>
+      <c r="D23" s="154">
+        <v>870928.3</v>
       </c>
       <c r="E23" s="80"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="120">
-        <v>-174514.13</v>
+      <c r="D24" s="154">
+        <v>-189426.91</v>
       </c>
       <c r="E24" s="80"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="120">
-        <v>0.73</v>
+      <c r="D25" s="154">
+        <v>0.61</v>
       </c>
       <c r="E25" s="80"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -2042,7 +2033,7 @@
       <c r="E26" s="80"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="57" t="s">
         <v>15</v>
       </c>
@@ -2050,12 +2041,12 @@
       <c r="C27" s="57"/>
       <c r="D27" s="121">
         <f>SUM(D23:D26)</f>
-        <v>624088</v>
+        <v>681502</v>
       </c>
       <c r="E27" s="81"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="3.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2063,7 +2054,7 @@
       <c r="E28" s="80"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -2071,19 +2062,19 @@
       <c r="E29" s="80"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="57" t="s">
         <v>15</v>
       </c>
       <c r="B30" s="57"/>
       <c r="C30" s="57"/>
-      <c r="D30" s="132">
+      <c r="D30" s="131">
         <f>SUM(D28:D29)</f>
         <v>0</v>
       </c>
       <c r="E30" s="81"/>
     </row>
-    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
         <v>16</v>
       </c>
@@ -2092,11 +2083,11 @@
       <c r="D31" s="122"/>
       <c r="E31" s="82">
         <f>D27+D30</f>
-        <v>624088</v>
+        <v>681502</v>
       </c>
       <c r="F31" s="15"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>17</v>
       </c>
@@ -2105,771 +2096,752 @@
       <c r="D32" s="123"/>
       <c r="E32" s="83"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C33" s="5"/>
-      <c r="D33" s="189">
+      <c r="D33" s="154">
         <v>40000</v>
       </c>
       <c r="E33" s="84"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="64" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="154">
+        <v>130000</v>
+      </c>
+      <c r="E34" s="84"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="120">
+      <c r="B35" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="154">
         <v>135100</v>
       </c>
-      <c r="E34" s="84"/>
-      <c r="H34" t="s">
+      <c r="E35" s="84"/>
+      <c r="H35" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="23" t="s">
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="85">
-        <f>SUM(D33:D34)</f>
-        <v>175100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="85">
+        <f>SUM(D33:D35)</f>
+        <v>305100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="125"/>
-      <c r="E36" s="66"/>
-    </row>
-    <row r="37" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="160" t="s">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="66"/>
+    </row>
+    <row r="38" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="158"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="126">
+      <c r="B38" s="159"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="186">
         <v>87562.7</v>
       </c>
-      <c r="E37" s="106"/>
-    </row>
-    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="160" t="s">
+      <c r="E38" s="106"/>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="B38" s="158"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="127">
+      <c r="B39" s="159"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="153">
         <v>6646.91</v>
       </c>
-      <c r="E38" s="106"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="23" t="s">
+      <c r="E39" s="106"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="124"/>
-      <c r="E39" s="86">
-        <f>SUM(D37:D38)</f>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="124"/>
+      <c r="E40" s="86">
+        <f>SUM(D38:D39)</f>
         <v>94209.61</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="32" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="128"/>
-      <c r="E40" s="87"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="87"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="188">
+      <c r="B42" s="5"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="153">
         <v>385570.28</v>
       </c>
-      <c r="E41" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="G41" s="104"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="E42" s="107" t="s">
+        <v>157</v>
+      </c>
+      <c r="G42" s="104"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="188">
+      <c r="C43" s="5"/>
+      <c r="D43" s="153">
         <v>19965.03</v>
       </c>
-      <c r="E42" s="108" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="str">
-        <f>A42</f>
-        <v>Sindicatos mes de SEPTIEMBRE</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="188">
-        <v>64395.09</v>
-      </c>
-      <c r="E43" s="108" t="str">
-        <f>E42</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E43" s="108" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="153">
+        <v>64395.09</v>
+      </c>
+      <c r="E44" s="108" t="str">
+        <f>E43</f>
+        <v>Debito 12/09</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="str">
+        <f>A44</f>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="188">
+      <c r="C45" s="5"/>
+      <c r="D45" s="153">
         <v>3993.01</v>
       </c>
-      <c r="E44" s="109" t="str">
-        <f>E43</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="23" t="s">
+      <c r="E45" s="109" t="str">
+        <f>E44</f>
+        <v>Debito 12/09</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="23" t="s">
         <v>30</v>
-      </c>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="129"/>
-      <c r="E45" s="86">
-        <f>SUM(D41:D44)</f>
-        <v>473923.41000000003</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="32" t="s">
-        <v>31</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="24"/>
       <c r="D46" s="128"/>
-      <c r="E46" s="87"/>
-    </row>
-    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="188">
-        <v>44625</v>
-      </c>
-      <c r="E47" s="90" t="s">
-        <v>164</v>
-      </c>
-      <c r="G47" s="112"/>
-    </row>
-    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>32</v>
+      <c r="E46" s="86">
+        <f>SUM(D42:D45)</f>
+        <v>473923.41000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="127"/>
+      <c r="E47" s="87"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="53" t="s">
+        <v>153</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="127">
-        <f>180470.49-86610.08</f>
-        <v>93860.409999999989</v>
+      <c r="D48" s="153">
+        <v>44625</v>
       </c>
       <c r="E48" s="90" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="G48" s="112"/>
+    </row>
+    <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="127">
-        <v>23426.2</v>
+      <c r="D49" s="153">
+        <v>102510.59</v>
       </c>
       <c r="E49" s="90" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="127">
-        <v>30000</v>
-      </c>
-      <c r="E50" s="90" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D50" s="126" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="90"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>143</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="188">
+      <c r="D51" s="153">
         <v>35000</v>
       </c>
       <c r="E51" s="90" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="161" t="s">
-        <v>163</v>
-      </c>
-      <c r="B52" s="162"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="188">
-        <v>310000</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="158" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="159"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="187">
+        <v>71000</v>
       </c>
       <c r="E52" s="90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="157" t="s">
-        <v>142</v>
-      </c>
-      <c r="B53" s="158"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="152"/>
-      <c r="E53" s="108"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="23" t="s">
         <v>34</v>
+      </c>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="86">
+        <f>SUM(D48:D52)</f>
+        <v>253135.59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="32" t="s">
+        <v>35</v>
       </c>
       <c r="B54" s="23"/>
       <c r="C54" s="23"/>
       <c r="D54" s="124"/>
-      <c r="E54" s="86">
-        <f>SUM(D47:D53)</f>
-        <v>536911.61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="124"/>
-      <c r="E55" s="89"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="53"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="88"/>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="23" t="s">
+      <c r="E54" s="89"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="53"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="88"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="92">
-        <f>SUM(D56:D56)</f>
+      <c r="B56" s="32"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="92">
+        <f>SUM(D55:D55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="32" t="s">
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B58" s="65"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="122"/>
-      <c r="E58" s="89"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="65"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="122"/>
+      <c r="E57" s="89"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="153">
+        <v>40649.81</v>
+      </c>
+      <c r="E58" s="93"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="127">
-        <v>45769.760000000002</v>
-      </c>
-      <c r="E59" s="93"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="127">
+      <c r="D59" s="153">
         <v>56000</v>
       </c>
-      <c r="E60" s="91"/>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="52" t="s">
+      <c r="E59" s="91"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="B61" s="52"/>
-      <c r="C61" s="52"/>
-      <c r="D61" s="94"/>
-      <c r="E61" s="86">
-        <f>SUM(D59:D60)</f>
-        <v>101769.76000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="80"/>
-      <c r="E62" s="95"/>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="25" t="s">
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="86">
+        <f>SUM(D58:D59)</f>
+        <v>96649.81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="95"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="97">
-        <f>3200000-2179746.24</f>
-        <v>1020253.7599999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="1"/>
-      <c r="D64" s="98"/>
-      <c r="E64" s="99"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="96"/>
+      <c r="E62" s="97">
+        <f>4000000-1904520.42</f>
+        <v>2095479.58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="D63" s="98"/>
+      <c r="E63" s="99"/>
+      <c r="F63" s="43"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="10"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="100"/>
+      <c r="E64" s="101">
+        <f>(SUM(E31:E62))</f>
+        <v>4000000</v>
+      </c>
       <c r="F64" s="43"/>
-    </row>
-    <row r="65" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="10"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="100"/>
-      <c r="E65" s="101">
-        <f>(SUM(E31:E63))</f>
-        <v>3026256.1499999994</v>
-      </c>
-      <c r="F65" s="43"/>
+      <c r="G64" s="112"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D65" s="98"/>
+      <c r="E65" s="98"/>
       <c r="G65" s="112"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D66" s="98"/>
       <c r="E66" s="98"/>
-      <c r="G66" s="112"/>
-    </row>
-    <row r="67" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D67" s="98"/>
-      <c r="E67" s="98"/>
-    </row>
-    <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="11" t="s">
+    </row>
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="12"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="102"/>
-      <c r="E68" s="103"/>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="157" t="s">
-        <v>154</v>
-      </c>
-      <c r="B69" s="165"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="169">
+      <c r="B67" s="12"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="102"/>
+      <c r="E67" s="103"/>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="158" t="s">
+        <v>161</v>
+      </c>
+      <c r="B68" s="160"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="164">
         <v>181000</v>
       </c>
-      <c r="E69" s="171"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="166"/>
-      <c r="B70" s="167"/>
+      <c r="E68" s="166"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="161"/>
+      <c r="B69" s="162"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="165"/>
+      <c r="E69" s="167"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="158"/>
+      <c r="B70" s="159"/>
       <c r="C70" s="53"/>
-      <c r="D70" s="170"/>
-      <c r="E70" s="172"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="157"/>
-      <c r="B71" s="158"/>
-      <c r="C71" s="53"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="131"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="50"/>
-      <c r="B72" s="49"/>
-      <c r="C72" s="49"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="154">
-        <f>SUM(D69:D71)</f>
+      <c r="D70" s="34"/>
+      <c r="E70" s="130"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="50"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="152">
+        <f>SUM(D68:D70)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="25" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="113"/>
-    </row>
-    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="113"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="67">
-        <f>E72+E74</f>
+      <c r="B75" s="10"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="67">
+        <f>E71+E73</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" s="79">
+        <f>E64</f>
+        <v>4000000</v>
+      </c>
+      <c r="D77" s="43"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B78" s="79">
-        <f>E65</f>
-        <v>3026256.1499999994</v>
-      </c>
-      <c r="D78" s="43"/>
-    </row>
-    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E64-E62</f>
+        <v>1904520.42</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B79" s="79">
-        <f>E65-E63</f>
-        <v>2006002.3899999997</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E75-E73</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B80" s="79">
-        <f>E76-E74</f>
+        <f>E75</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="B81" s="79">
-        <f>E76</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="163"/>
+    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="155"/>
+      <c r="B83" s="156"/>
+      <c r="C83" s="156"/>
+      <c r="D83" s="156"/>
+      <c r="E83" s="156"/>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="156"/>
       <c r="B84" s="156"/>
       <c r="C84" s="156"/>
       <c r="D84" s="156"/>
       <c r="E84" s="156"/>
     </row>
-    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="156"/>
       <c r="B85" s="156"/>
       <c r="C85" s="156"/>
       <c r="D85" s="156"/>
       <c r="E85" s="156"/>
     </row>
-    <row r="86" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="156"/>
-      <c r="B86" s="156"/>
-      <c r="C86" s="156"/>
-      <c r="D86" s="156"/>
-      <c r="E86" s="156"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="16" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B88" s="38"/>
-      <c r="C88" s="17"/>
-    </row>
-    <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="28" t="s">
+      <c r="B87" s="38"/>
+      <c r="C87" s="17"/>
+    </row>
+    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B89" s="111">
-        <v>-705431.13749999925</v>
-      </c>
-      <c r="C89" s="19"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B88" s="111">
+        <v>-421384.30749999965</v>
+      </c>
+      <c r="C88" s="19"/>
+    </row>
+    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B89" s="39">
+        <f>PRORRATEO!H25</f>
+        <v>2730143.9299999997</v>
+      </c>
+      <c r="C89" s="17"/>
+    </row>
+    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B90" s="39">
-        <f>PRORRATEO!H25</f>
-        <v>2907739.07</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B90" s="47"/>
       <c r="C90" s="17"/>
     </row>
-    <row r="91" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="18" t="s">
-        <v>51</v>
+    <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="150" t="s">
+        <v>146</v>
       </c>
       <c r="B91" s="47"/>
       <c r="C91" s="17"/>
     </row>
-    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="151" t="s">
-        <v>146</v>
-      </c>
-      <c r="B92" s="47">
-        <v>-946</v>
-      </c>
+    <row r="92" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="150" t="s">
+        <v>148</v>
+      </c>
+      <c r="B92" s="47"/>
       <c r="C92" s="17"/>
     </row>
-    <row r="93" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="151" t="s">
-        <v>157</v>
-      </c>
-      <c r="B93" s="47">
-        <v>-262000</v>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" s="91">
+        <f>B112</f>
+        <v>0</v>
       </c>
       <c r="C93" s="17"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B94" s="91">
-        <f>B113</f>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" s="47">
+        <f>-B78</f>
+        <v>-1904520.42</v>
+      </c>
+      <c r="C94" s="17"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B95" s="47">
+        <f>-(B79)</f>
+        <v>-181000</v>
+      </c>
+      <c r="C95" s="17"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" s="110">
+        <f>SUM(B88:B95)</f>
+        <v>223239.20250000013</v>
+      </c>
+      <c r="C96" s="20"/>
+    </row>
+    <row r="97" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="40"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="43"/>
+    </row>
+    <row r="98" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="41"/>
+      <c r="C98" s="20"/>
+    </row>
+    <row r="99" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="40"/>
+      <c r="C99" s="35"/>
+    </row>
+    <row r="100" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B100" s="33"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="46"/>
+    </row>
+    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B101" s="34">
         <v>0</v>
       </c>
-      <c r="C94" s="17"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="37" t="s">
+      <c r="C101" s="35"/>
+    </row>
+    <row r="102" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="33">
+        <v>0</v>
+      </c>
+      <c r="C102" s="20"/>
+      <c r="D102" s="43"/>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B95" s="47">
-        <f>-B79</f>
-        <v>-2006002.3899999997</v>
-      </c>
-      <c r="C95" s="17"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B96" s="47">
-        <f>-(B80)</f>
-        <v>-181000</v>
-      </c>
-      <c r="C96" s="17"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B97" s="110">
-        <f>SUM(B89:B96)</f>
-        <v>-247640.45749999909</v>
-      </c>
-      <c r="C97" s="20"/>
-    </row>
-    <row r="98" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="40"/>
-      <c r="C98" s="20"/>
-      <c r="D98" s="43"/>
-    </row>
-    <row r="99" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="41"/>
-      <c r="C99" s="20"/>
-    </row>
-    <row r="100" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="40"/>
-      <c r="C100" s="35"/>
-    </row>
-    <row r="101" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B101" s="33"/>
-      <c r="C101" s="35"/>
-      <c r="D101" s="46"/>
-    </row>
-    <row r="102" spans="1:4" s="36" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B102" s="34">
-        <v>0</v>
-      </c>
-      <c r="C102" s="35"/>
-    </row>
-    <row r="103" spans="1:4" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="B103" s="33">
         <v>0</v>
       </c>
       <c r="C103" s="20"/>
-      <c r="D103" s="43"/>
-    </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B104" s="33">
         <v>0</v>
       </c>
-      <c r="C104" s="20"/>
-    </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B105" s="33">
+      <c r="C104" s="22"/>
+    </row>
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" s="48">
+        <f>SUM(B101:B104)</f>
         <v>0</v>
       </c>
-      <c r="C105" s="22"/>
-    </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B106" s="48">
-        <f>SUM(B102:B105)</f>
-        <v>0</v>
-      </c>
-      <c r="C106" s="17"/>
-    </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="164" t="s">
+      <c r="C105" s="17"/>
+    </row>
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="157" t="s">
         <v>58</v>
       </c>
+      <c r="B108" s="156"/>
+      <c r="C108" s="156"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="156"/>
       <c r="B109" s="156"/>
       <c r="C109" s="156"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="156"/>
-      <c r="B110" s="156"/>
-      <c r="C110" s="156"/>
-    </row>
-    <row r="111" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="55"/>
+      <c r="B110" s="33"/>
+      <c r="C110" s="33">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="55"/>
       <c r="B111" s="33"/>
-      <c r="C111" s="33">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="55"/>
-      <c r="B112" s="33"/>
-      <c r="C112" s="40"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="44" t="s">
+      <c r="C111" s="40"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B113" s="105">
-        <f>SUM(B111:B112)</f>
+      <c r="B112" s="105">
+        <f>SUM(B110:B111)</f>
         <v>0</v>
       </c>
-      <c r="C113" s="45"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M114" s="8"/>
-    </row>
-    <row r="115" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="168"/>
+      <c r="C112" s="45"/>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M113" s="8"/>
+    </row>
+    <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="163"/>
+      <c r="B114" s="156"/>
+      <c r="C114" s="156"/>
+      <c r="D114" s="156"/>
+      <c r="E114" s="156"/>
+    </row>
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="156"/>
       <c r="B115" s="156"/>
       <c r="C115" s="156"/>
       <c r="D115" s="156"/>
       <c r="E115" s="156"/>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="156"/>
       <c r="B116" s="156"/>
       <c r="C116" s="156"/>
       <c r="D116" s="156"/>
       <c r="E116" s="156"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="156"/>
       <c r="B117" s="156"/>
       <c r="C117" s="156"/>
       <c r="D117" s="156"/>
       <c r="E117" s="156"/>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="156"/>
-      <c r="B118" s="156"/>
-      <c r="C118" s="156"/>
-      <c r="D118" s="156"/>
-      <c r="E118" s="156"/>
-    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A84:E86"/>
-    <mergeCell ref="A109:C110"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A69:B70"/>
-    <mergeCell ref="A115:E118"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
+  <mergeCells count="12">
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A83:E85"/>
+    <mergeCell ref="A108:C109"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A68:B69"/>
+    <mergeCell ref="A114:E117"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2880,30 +2852,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.109375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" customWidth="1"/>
-    <col min="9" max="9" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" customWidth="1"/>
-    <col min="12" max="12" width="11.33203125" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="10.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.28515625" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="13.5546875" customWidth="1"/>
-    <col min="17" max="17" width="4.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2911,7 +2883,7 @@
         <v>59</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="177" t="s">
+      <c r="F1" s="183" t="s">
         <v>60</v>
       </c>
       <c r="G1" s="156"/>
@@ -2925,7 +2897,7 @@
       <c r="O1" s="156"/>
       <c r="P1" s="6"/>
     </row>
-    <row r="2" spans="1:20" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -2945,14 +2917,14 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="182">
+      <c r="O2" s="177">
         <f>T4</f>
-        <v>3200000</v>
+        <v>4000000</v>
       </c>
       <c r="P2" s="156"/>
       <c r="Q2" s="15"/>
     </row>
-    <row r="3" spans="1:20" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2971,17 +2943,17 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="186">
+      <c r="O3" s="181">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="187"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="180" t="s">
+      <c r="P3" s="182"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="171" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="183" t="s">
+      <c r="B4" s="178" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="173" t="s">
@@ -2990,7 +2962,7 @@
       <c r="D4" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="175" t="s">
+      <c r="E4" s="174" t="s">
         <v>68</v>
       </c>
       <c r="F4" s="173" t="s">
@@ -3002,57 +2974,60 @@
       <c r="H4" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="175" t="s">
+      <c r="I4" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="178" t="s">
+      <c r="J4" s="184" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="181" t="s">
+      <c r="K4" s="176" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="L4" s="185" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="181" t="s">
+      <c r="M4" s="176" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="181" t="s">
+      <c r="N4" s="176" t="s">
         <v>77</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="185" t="s">
+      <c r="P4" s="180" t="s">
         <v>79</v>
       </c>
       <c r="S4" s="43"/>
       <c r="T4">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="174"/>
-      <c r="B5" s="184"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="176"/>
-      <c r="N5" s="176"/>
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="172"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="172"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/10</v>
       </c>
-      <c r="P5" s="174"/>
-    </row>
-    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P5" s="172"/>
+      <c r="T5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>80</v>
       </c>
@@ -3071,12 +3046,12 @@
       <c r="F6" s="68">
         <v>3</v>
       </c>
-      <c r="G6" s="134">
-        <v>95430.1</v>
-      </c>
-      <c r="H6" s="130">
+      <c r="G6" s="133">
+        <v>101430.1</v>
+      </c>
+      <c r="H6" s="129">
         <f>G6</f>
-        <v>95430.1</v>
+        <v>101430.1</v>
       </c>
       <c r="I6" s="70"/>
       <c r="J6" s="117">
@@ -3093,19 +3068,19 @@
       </c>
       <c r="M6" s="72">
         <f t="shared" ref="M6:M24" si="3">O$2*F6%</f>
-        <v>96000</v>
+        <v>120000</v>
       </c>
       <c r="N6" s="114">
         <f t="shared" ref="N6:N24" si="4">SUM(J6:M6)</f>
-        <v>101430</v>
+        <v>125430</v>
       </c>
       <c r="O6" s="118" t="str">
         <f t="shared" ref="O6:O24" si="5">CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
-        <v>$101430,1</v>
+        <v>$125430,1</v>
       </c>
       <c r="P6" s="119" t="str">
         <f t="shared" ref="P6:P24" si="6">CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
-        <v>$104473,1</v>
+        <v>$129193,1</v>
       </c>
       <c r="Q6" s="43" t="str">
         <f t="shared" ref="Q6:Q24" si="7">CONCATENATE(B6)</f>
@@ -3115,7 +3090,7 @@
         <v>181000</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>84</v>
       </c>
@@ -3134,12 +3109,12 @@
       <c r="F7" s="68">
         <v>3.8</v>
       </c>
-      <c r="G7" s="134">
-        <v>120878.2</v>
-      </c>
-      <c r="H7" s="130">
+      <c r="G7" s="133">
+        <v>128478.2</v>
+      </c>
+      <c r="H7" s="129">
         <f>G7</f>
-        <v>120878.2</v>
+        <v>128478.2</v>
       </c>
       <c r="I7" s="70"/>
       <c r="J7" s="117">
@@ -3156,19 +3131,19 @@
       </c>
       <c r="M7" s="72">
         <f t="shared" si="3"/>
-        <v>121600</v>
+        <v>152000</v>
       </c>
       <c r="N7" s="114">
         <f t="shared" si="4"/>
-        <v>128478</v>
+        <v>158878</v>
       </c>
       <c r="O7" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$128478,2</v>
+        <v>$158878,2</v>
       </c>
       <c r="P7" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$132332,2</v>
+        <v>$163644,2</v>
       </c>
       <c r="Q7" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3176,7 +3151,7 @@
       </c>
       <c r="R7" s="43"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>84</v>
       </c>
@@ -3195,18 +3170,20 @@
       <c r="F8" s="68">
         <v>3</v>
       </c>
-      <c r="G8" s="134">
-        <v>95430.3</v>
-      </c>
-      <c r="H8" s="130"/>
+      <c r="G8" s="133">
+        <v>201632.3</v>
+      </c>
+      <c r="H8" s="129">
+        <v>98293.3</v>
+      </c>
       <c r="I8" s="70"/>
       <c r="J8" s="117">
         <f t="shared" si="0"/>
-        <v>95430.3</v>
+        <v>103338.99999999999</v>
       </c>
       <c r="K8" s="71">
         <f t="shared" si="1"/>
-        <v>4771.5150000000003</v>
+        <v>5166.95</v>
       </c>
       <c r="L8" s="72">
         <f t="shared" si="2"/>
@@ -3214,26 +3191,26 @@
       </c>
       <c r="M8" s="72">
         <f t="shared" si="3"/>
-        <v>96000</v>
+        <v>120000</v>
       </c>
       <c r="N8" s="114">
         <f t="shared" si="4"/>
-        <v>201631.815</v>
+        <v>233935.94999999998</v>
       </c>
       <c r="O8" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$201632,3</v>
+        <v>$233936,3</v>
       </c>
       <c r="P8" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$207681,3</v>
+        <v>$240954,3</v>
       </c>
       <c r="Q8" s="43" t="str">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>91</v>
       </c>
@@ -3252,18 +3229,18 @@
       <c r="F9" s="68">
         <v>3.1</v>
       </c>
-      <c r="G9" s="134">
-        <v>98611.4</v>
-      </c>
-      <c r="H9" s="130"/>
+      <c r="G9" s="133">
+        <v>208353.4</v>
+      </c>
+      <c r="H9" s="129"/>
       <c r="I9" s="70"/>
       <c r="J9" s="117">
         <f t="shared" si="0"/>
-        <v>98611.4</v>
+        <v>208353.4</v>
       </c>
       <c r="K9" s="71">
         <f t="shared" si="1"/>
-        <v>4930.57</v>
+        <v>10417.67</v>
       </c>
       <c r="L9" s="72">
         <f t="shared" si="2"/>
@@ -3271,19 +3248,19 @@
       </c>
       <c r="M9" s="72">
         <f t="shared" si="3"/>
-        <v>99200</v>
+        <v>124000</v>
       </c>
       <c r="N9" s="114">
         <f t="shared" si="4"/>
-        <v>208352.97</v>
+        <v>348382.07</v>
       </c>
       <c r="O9" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$208353,4</v>
+        <v>$348382,4</v>
       </c>
       <c r="P9" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$214604,4</v>
+        <v>$358834,4</v>
       </c>
       <c r="Q9" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3291,7 +3268,7 @@
       </c>
       <c r="S9" s="43"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>91</v>
       </c>
@@ -3310,18 +3287,18 @@
       <c r="F10" s="68">
         <v>3.1</v>
       </c>
-      <c r="G10" s="134">
-        <v>202153.5</v>
-      </c>
-      <c r="H10" s="130"/>
+      <c r="G10" s="133">
+        <v>317072.5</v>
+      </c>
+      <c r="H10" s="129"/>
       <c r="I10" s="70"/>
       <c r="J10" s="117">
         <f t="shared" si="0"/>
-        <v>202153.5</v>
+        <v>317072.5</v>
       </c>
       <c r="K10" s="71">
         <f t="shared" si="1"/>
-        <v>10107.675000000001</v>
+        <v>15853.625</v>
       </c>
       <c r="L10" s="72">
         <f t="shared" si="2"/>
@@ -3329,19 +3306,19 @@
       </c>
       <c r="M10" s="72">
         <f t="shared" si="3"/>
-        <v>99200</v>
+        <v>124000</v>
       </c>
       <c r="N10" s="114">
         <f t="shared" si="4"/>
-        <v>317072.17499999999</v>
+        <v>462537.125</v>
       </c>
       <c r="O10" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$317072,5</v>
+        <v>$462537,5</v>
       </c>
       <c r="P10" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$326584,5</v>
+        <v>$476413,5</v>
       </c>
       <c r="Q10" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3349,7 +3326,7 @@
       </c>
       <c r="S10" s="43"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>98</v>
       </c>
@@ -3366,12 +3343,12 @@
       <c r="F11" s="68">
         <v>3.2</v>
       </c>
-      <c r="G11" s="134">
-        <v>101792.6</v>
-      </c>
-      <c r="H11" s="130">
+      <c r="G11" s="133">
+        <v>108192.6</v>
+      </c>
+      <c r="H11" s="129">
         <f>G11</f>
-        <v>101792.6</v>
+        <v>108192.6</v>
       </c>
       <c r="I11" s="70"/>
       <c r="J11" s="117">
@@ -3388,26 +3365,26 @@
       </c>
       <c r="M11" s="72">
         <f t="shared" si="3"/>
-        <v>102400</v>
+        <v>128000</v>
       </c>
       <c r="N11" s="114">
         <f t="shared" si="4"/>
-        <v>108192</v>
+        <v>133792</v>
       </c>
       <c r="O11" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$108192,6</v>
+        <v>$133792,6</v>
       </c>
       <c r="P11" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$111438,6</v>
+        <v>$137806,6</v>
       </c>
       <c r="Q11" s="43" t="str">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>98</v>
       </c>
@@ -3426,12 +3403,12 @@
       <c r="F12" s="68">
         <v>3.3</v>
       </c>
-      <c r="G12" s="134">
-        <v>104973.7</v>
-      </c>
-      <c r="H12" s="130">
+      <c r="G12" s="133">
+        <v>111573.7</v>
+      </c>
+      <c r="H12" s="129">
         <f>G12</f>
-        <v>104973.7</v>
+        <v>111573.7</v>
       </c>
       <c r="I12" s="70"/>
       <c r="J12" s="117">
@@ -3448,26 +3425,26 @@
       </c>
       <c r="M12" s="72">
         <f t="shared" si="3"/>
-        <v>105600</v>
+        <v>132000</v>
       </c>
       <c r="N12" s="114">
         <f t="shared" si="4"/>
-        <v>111573</v>
+        <v>137973</v>
       </c>
       <c r="O12" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$111573,7</v>
+        <v>$137973,7</v>
       </c>
       <c r="P12" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$114920,7</v>
+        <v>$142112,7</v>
       </c>
       <c r="Q12" s="43" t="str">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>104</v>
       </c>
@@ -3486,17 +3463,17 @@
       <c r="F13" s="68">
         <v>6.3</v>
       </c>
-      <c r="G13" s="134">
-        <v>212376.23</v>
+      <c r="G13" s="133">
+        <v>212403.23</v>
       </c>
       <c r="H13" s="69">
-        <f>189000+23976.23</f>
-        <v>212976.23</v>
+        <f>201600+11403</f>
+        <v>213003</v>
       </c>
       <c r="I13" s="70"/>
       <c r="J13" s="117">
         <f t="shared" si="0"/>
-        <v>-600</v>
+        <v>-599.76999999998952</v>
       </c>
       <c r="K13" s="71">
         <f t="shared" si="1"/>
@@ -3508,19 +3485,19 @@
       </c>
       <c r="M13" s="72">
         <f t="shared" si="3"/>
-        <v>201600</v>
+        <v>252000</v>
       </c>
       <c r="N13" s="114">
         <f t="shared" si="4"/>
-        <v>212403</v>
+        <v>262803.23</v>
       </c>
       <c r="O13" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$212403,23</v>
+        <v>$262803,23</v>
       </c>
       <c r="P13" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$218775,23</v>
+        <v>$270687,23</v>
       </c>
       <c r="Q13" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3530,7 +3507,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>104</v>
       </c>
@@ -3549,12 +3526,12 @@
       <c r="F14" s="68">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G14" s="134">
-        <v>162231.22</v>
+      <c r="G14" s="133">
+        <v>172431.22</v>
       </c>
       <c r="H14" s="69">
         <f>G14</f>
-        <v>162231.22</v>
+        <v>172431.22</v>
       </c>
       <c r="I14" s="70"/>
       <c r="J14" s="117">
@@ -3571,26 +3548,26 @@
       </c>
       <c r="M14" s="72">
         <f t="shared" si="3"/>
-        <v>163200</v>
+        <v>204000</v>
       </c>
       <c r="N14" s="114">
         <f t="shared" si="4"/>
-        <v>172431</v>
+        <v>213231</v>
       </c>
       <c r="O14" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$172431,22</v>
+        <v>$213231,22</v>
       </c>
       <c r="P14" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$177604,22</v>
+        <v>$219628,22</v>
       </c>
       <c r="Q14" s="43" t="str">
         <f t="shared" si="7"/>
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>112</v>
       </c>
@@ -3607,16 +3584,17 @@
       <c r="F15" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G15" s="134">
-        <v>260842.21</v>
+      <c r="G15" s="133">
+        <v>269417.21000000002</v>
       </c>
       <c r="H15" s="69">
-        <v>268667.21000000002</v>
+        <f>G15</f>
+        <v>269417.21000000002</v>
       </c>
       <c r="I15" s="70"/>
       <c r="J15" s="117">
         <f t="shared" si="0"/>
-        <v>-7825.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="K15" s="71">
         <f t="shared" si="1"/>
@@ -3628,26 +3606,26 @@
       </c>
       <c r="M15" s="72">
         <f t="shared" si="3"/>
-        <v>262399.99999999994</v>
+        <v>327999.99999999994</v>
       </c>
       <c r="N15" s="114">
         <f t="shared" si="4"/>
-        <v>269416.99999999988</v>
+        <v>342841.99999999994</v>
       </c>
       <c r="O15" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$269417,21</v>
+        <v>$342842,21</v>
       </c>
       <c r="P15" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$277500,21</v>
+        <v>$353127,21</v>
       </c>
       <c r="Q15" s="43" t="str">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>112</v>
       </c>
@@ -3666,12 +3644,12 @@
       <c r="F16" s="68">
         <v>6.1</v>
       </c>
-      <c r="G16" s="134">
-        <v>194041.14</v>
+      <c r="G16" s="133">
+        <v>206241.14</v>
       </c>
       <c r="H16" s="69">
         <f>G16</f>
-        <v>194041.14</v>
+        <v>206241.14</v>
       </c>
       <c r="I16" s="70"/>
       <c r="J16" s="117">
@@ -3688,26 +3666,26 @@
       </c>
       <c r="M16" s="72">
         <f t="shared" si="3"/>
-        <v>195200</v>
+        <v>244000</v>
       </c>
       <c r="N16" s="114">
         <f t="shared" si="4"/>
-        <v>206241</v>
+        <v>255041</v>
       </c>
       <c r="O16" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$206241,14</v>
+        <v>$255041,14</v>
       </c>
       <c r="P16" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$212428,14</v>
+        <v>$262692,14</v>
       </c>
       <c r="Q16" s="43" t="str">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>118</v>
       </c>
@@ -3724,16 +3702,17 @@
       <c r="F17" s="68">
         <v>5</v>
       </c>
-      <c r="G17" s="134">
-        <v>154398.13</v>
+      <c r="G17" s="133">
+        <v>169351.13</v>
       </c>
       <c r="H17" s="69">
-        <v>159030.13</v>
+        <f>G17</f>
+        <v>169351.13</v>
       </c>
       <c r="I17" s="70"/>
       <c r="J17" s="117">
         <f t="shared" si="0"/>
-        <v>-4632</v>
+        <v>0</v>
       </c>
       <c r="K17" s="71">
         <f t="shared" si="1"/>
@@ -3745,26 +3724,26 @@
       </c>
       <c r="M17" s="72">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="N17" s="114">
         <f t="shared" si="4"/>
-        <v>164418</v>
+        <v>209050</v>
       </c>
       <c r="O17" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$164418,13</v>
+        <v>$209050,13</v>
       </c>
       <c r="P17" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$169351,13</v>
+        <v>$215322,13</v>
       </c>
       <c r="Q17" s="43" t="str">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>118</v>
       </c>
@@ -3783,20 +3762,20 @@
       <c r="F18" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G18" s="134">
-        <v>15065931.119999999</v>
+      <c r="G18" s="133">
+        <v>15822586.119999999</v>
       </c>
       <c r="H18" s="69">
-        <v>260842</v>
+        <v>277242</v>
       </c>
       <c r="I18" s="70"/>
       <c r="J18" s="117">
         <f t="shared" si="0"/>
-        <v>14805089.119999999</v>
+        <v>15545344.119999999</v>
       </c>
       <c r="K18" s="71">
         <f t="shared" si="1"/>
-        <v>740254.45600000001</v>
+        <v>777267.20600000001</v>
       </c>
       <c r="L18" s="72">
         <f t="shared" si="2"/>
@@ -3804,26 +3783,26 @@
       </c>
       <c r="M18" s="72">
         <f t="shared" si="3"/>
-        <v>262399.99999999994</v>
+        <v>327999.99999999994</v>
       </c>
       <c r="N18" s="114">
         <f t="shared" si="4"/>
-        <v>15822585.575999999</v>
+        <v>16665453.325999999</v>
       </c>
       <c r="O18" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$15822586,12</v>
+        <v>$16665453,12</v>
       </c>
       <c r="P18" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$16297263,12</v>
+        <v>$17165417,12</v>
       </c>
       <c r="Q18" s="43" t="str">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>124</v>
       </c>
@@ -3840,18 +3819,18 @@
       <c r="F19" s="68">
         <v>6.1</v>
       </c>
-      <c r="G19" s="134">
-        <v>10897785.17</v>
+      <c r="G19" s="133">
+        <v>11648915.17</v>
       </c>
       <c r="H19" s="69"/>
       <c r="I19" s="70"/>
       <c r="J19" s="117">
         <f t="shared" si="0"/>
-        <v>10897785.17</v>
+        <v>11648915.17</v>
       </c>
       <c r="K19" s="71">
         <f t="shared" si="1"/>
-        <v>544889.2585</v>
+        <v>582445.7585</v>
       </c>
       <c r="L19" s="72">
         <f t="shared" si="2"/>
@@ -3859,26 +3838,26 @@
       </c>
       <c r="M19" s="72">
         <f t="shared" si="3"/>
-        <v>195200</v>
+        <v>244000</v>
       </c>
       <c r="N19" s="114">
         <f t="shared" si="4"/>
-        <v>11648915.4285</v>
+        <v>12486401.9285</v>
       </c>
       <c r="O19" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$11648915,17</v>
+        <v>$12486402,17</v>
       </c>
       <c r="P19" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$11998383,17</v>
+        <v>$12860994,17</v>
       </c>
       <c r="Q19" s="43" t="str">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>124</v>
       </c>
@@ -3897,16 +3876,16 @@
       <c r="F20" s="68">
         <v>5</v>
       </c>
-      <c r="G20" s="135">
-        <v>159050.16</v>
-      </c>
-      <c r="H20" s="130">
-        <v>160000</v>
+      <c r="G20" s="134">
+        <v>173143.16</v>
+      </c>
+      <c r="H20" s="129">
+        <v>174000</v>
       </c>
       <c r="I20" s="70"/>
       <c r="J20" s="117">
         <f t="shared" si="0"/>
-        <v>-949.83999999999651</v>
+        <v>-856.83999999999651</v>
       </c>
       <c r="K20" s="71">
         <f t="shared" si="1"/>
@@ -3918,19 +3897,19 @@
       </c>
       <c r="M20" s="72">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="N20" s="114">
         <f t="shared" si="4"/>
-        <v>168100.16</v>
+        <v>208193.16</v>
       </c>
       <c r="O20" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$168100,16</v>
+        <v>$208193,16</v>
       </c>
       <c r="P20" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$173143,16</v>
+        <v>$214439,16</v>
       </c>
       <c r="Q20" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3940,7 +3919,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>129</v>
       </c>
@@ -3957,17 +3936,17 @@
       <c r="F21" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G21" s="134">
-        <v>280706.15000000002</v>
+      <c r="G21" s="133">
+        <v>273166.15000000002</v>
       </c>
       <c r="H21" s="69">
-        <f>18918+264918.15+946</f>
-        <v>284782.15000000002</v>
+        <f>G21</f>
+        <v>273166.15000000002</v>
       </c>
       <c r="I21" s="70"/>
       <c r="J21" s="117">
         <f t="shared" si="0"/>
-        <v>-4076</v>
+        <v>0</v>
       </c>
       <c r="K21" s="71">
         <f t="shared" si="1"/>
@@ -3979,19 +3958,19 @@
       </c>
       <c r="M21" s="72">
         <f t="shared" si="3"/>
-        <v>262399.99999999994</v>
+        <v>327999.99999999994</v>
       </c>
       <c r="N21" s="114">
         <f t="shared" si="4"/>
-        <v>273165.99999999994</v>
+        <v>342841.99999999994</v>
       </c>
       <c r="O21" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$273166,15</v>
+        <v>$342842,15</v>
       </c>
       <c r="P21" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$281361,15</v>
+        <v>$353127,15</v>
       </c>
       <c r="Q21" s="43" t="str">
         <f t="shared" si="7"/>
@@ -3999,7 +3978,7 @@
       </c>
       <c r="S21" s="42"/>
     </row>
-    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>129</v>
       </c>
@@ -4016,21 +3995,18 @@
       <c r="F22" s="68">
         <v>6.1</v>
       </c>
-      <c r="G22" s="135">
-        <v>194041.2</v>
-      </c>
-      <c r="H22" s="69">
-        <f>G22</f>
-        <v>194041.2</v>
-      </c>
+      <c r="G22" s="134">
+        <v>206241.2</v>
+      </c>
+      <c r="H22" s="69"/>
       <c r="I22" s="70"/>
       <c r="J22" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>206241.2</v>
       </c>
       <c r="K22" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10312.060000000001</v>
       </c>
       <c r="L22" s="72">
         <f t="shared" si="2"/>
@@ -4038,19 +4014,19 @@
       </c>
       <c r="M22" s="72">
         <f t="shared" si="3"/>
-        <v>195200</v>
+        <v>244000</v>
       </c>
       <c r="N22" s="114">
         <f t="shared" si="4"/>
-        <v>206241</v>
+        <v>471594.26</v>
       </c>
       <c r="O22" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$206241,20</v>
+        <v>$471594,20</v>
       </c>
       <c r="P22" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$212428,20</v>
+        <v>$485742,20</v>
       </c>
       <c r="Q22" s="43" t="str">
         <f t="shared" si="7"/>
@@ -4060,7 +4036,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>135</v>
       </c>
@@ -4079,21 +4055,20 @@
       <c r="F23" s="68">
         <v>5</v>
       </c>
-      <c r="G23" s="134">
-        <v>326053.19</v>
+      <c r="G23" s="133">
+        <v>169050.19</v>
       </c>
       <c r="H23" s="69">
-        <f>G23</f>
-        <v>326053.19</v>
+        <v>160000</v>
       </c>
       <c r="I23" s="70"/>
       <c r="J23" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9050.1900000000023</v>
       </c>
       <c r="K23" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>452.50950000000012</v>
       </c>
       <c r="L23" s="72">
         <f t="shared" si="2"/>
@@ -4101,26 +4076,29 @@
       </c>
       <c r="M23" s="72">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="N23" s="114">
         <f t="shared" si="4"/>
-        <v>169050</v>
+        <v>218552.69949999999</v>
       </c>
       <c r="O23" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$169050,19</v>
+        <v>$218553,19</v>
       </c>
       <c r="P23" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$174122,19</v>
+        <v>$225109,19</v>
       </c>
       <c r="Q23" s="43" t="str">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="S23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>135</v>
       </c>
@@ -4130,27 +4108,28 @@
       <c r="C24" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="D24" s="153" t="s">
+      <c r="D24" s="151" t="s">
         <v>139</v>
       </c>
       <c r="E24" s="63"/>
       <c r="F24" s="68">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G24" s="134">
-        <v>253017.18</v>
+      <c r="G24" s="133">
+        <v>268259.18</v>
       </c>
       <c r="H24" s="69">
-        <v>262000</v>
+        <f>267324.18</f>
+        <v>267324.18</v>
       </c>
       <c r="I24" s="70"/>
       <c r="J24" s="71">
         <f t="shared" si="0"/>
-        <v>-8982.820000000007</v>
+        <v>935</v>
       </c>
       <c r="K24" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="L24" s="72">
         <f t="shared" si="2"/>
@@ -4158,19 +4137,19 @@
       </c>
       <c r="M24" s="72">
         <f t="shared" si="3"/>
-        <v>262399.99999999994</v>
+        <v>327999.99999999994</v>
       </c>
       <c r="N24" s="114">
         <f t="shared" si="4"/>
-        <v>268259.17999999993</v>
+        <v>343823.74999999994</v>
       </c>
       <c r="O24" s="116" t="str">
         <f t="shared" si="5"/>
-        <v>$268259,18</v>
+        <v>$343824,18</v>
       </c>
       <c r="P24" s="119" t="str">
         <f t="shared" si="6"/>
-        <v>$276307,18</v>
+        <v>$354138,18</v>
       </c>
       <c r="Q24" s="43" t="str">
         <f t="shared" si="7"/>
@@ -4180,7 +4159,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="73"/>
       <c r="C25" s="74"/>
       <c r="D25" s="75"/>
@@ -4191,11 +4170,11 @@
       </c>
       <c r="G25" s="54">
         <f t="shared" si="8"/>
-        <v>28979742.899999995</v>
+        <v>30767937.899999995</v>
       </c>
       <c r="H25" s="60">
         <f t="shared" si="8"/>
-        <v>2907739.07</v>
+        <v>2730143.9299999997</v>
       </c>
       <c r="I25" s="54">
         <f t="shared" si="8"/>
@@ -4203,11 +4182,11 @@
       </c>
       <c r="J25" s="60">
         <f t="shared" si="8"/>
-        <v>26072003.829999998</v>
+        <v>28037793.970000003</v>
       </c>
       <c r="K25" s="60">
         <f t="shared" si="8"/>
-        <v>1304953.4745</v>
+        <v>1401962.5289999999</v>
       </c>
       <c r="L25" s="60">
         <f t="shared" si="8"/>
@@ -4215,7 +4194,7 @@
       </c>
       <c r="M25" s="60">
         <f t="shared" si="8"/>
-        <v>3200000</v>
+        <v>4000000</v>
       </c>
       <c r="N25" s="115"/>
       <c r="O25" s="77">
@@ -4227,14 +4206,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
       <c r="R26" s="104"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D28" s="168" t="s">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="163" t="s">
         <v>141</v>
       </c>
       <c r="E28" s="156"/>
@@ -4249,7 +4228,7 @@
       <c r="N28" s="156"/>
       <c r="O28" s="156"/>
     </row>
-    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="156"/>
       <c r="E29" s="156"/>
       <c r="F29" s="156"/>
@@ -4263,7 +4242,7 @@
       <c r="N29" s="156"/>
       <c r="O29" s="156"/>
     </row>
-    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="156"/>
       <c r="E30" s="156"/>
       <c r="F30" s="156"/>
@@ -4277,7 +4256,7 @@
       <c r="N30" s="156"/>
       <c r="O30" s="156"/>
     </row>
-    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="156"/>
       <c r="E31" s="156"/>
       <c r="F31" s="156"/>
@@ -4291,7 +4270,7 @@
       <c r="N31" s="156"/>
       <c r="O31" s="156"/>
     </row>
-    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="156"/>
       <c r="E32" s="156"/>
       <c r="F32" s="156"/>
@@ -4305,7 +4284,7 @@
       <c r="N32" s="156"/>
       <c r="O32" s="156"/>
     </row>
-    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="156"/>
       <c r="E33" s="156"/>
       <c r="F33" s="156"/>
@@ -4325,6 +4304,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4337,13 +4323,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>

--- a/PUEYRREDON 1494/Septiembre/PUEYRREDON Septiembre.xlsx
+++ b/PUEYRREDON 1494/Septiembre/PUEYRREDON Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48439119-F01D-4588-AE38-E3A92AA95D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C81F52F-A560-4D03-943F-005ACFF39144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1405,17 +1405,30 @@
     <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1430,26 +1443,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1467,19 +1480,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1919,54 +1919,52 @@
       <c r="E7" s="149"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="168" t="s">
+      <c r="B9" s="157" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="156"/>
+      <c r="C9" s="158"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="156"/>
-      <c r="C10" s="156"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="156"/>
-      <c r="C11" s="156"/>
+      <c r="B11" s="158"/>
+      <c r="C11" s="158"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="132">
-        <v>2</v>
-      </c>
+      <c r="B12" s="132"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="169" t="s">
+      <c r="A14" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="158"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="158"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="156"/>
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
+      <c r="A15" s="158"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="156"/>
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
-      <c r="E16" s="156"/>
+      <c r="A16" s="158"/>
+      <c r="B16" s="158"/>
+      <c r="C16" s="158"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="158"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="156"/>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
+      <c r="A17" s="158"/>
+      <c r="B17" s="158"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="158"/>
+      <c r="E17" s="158"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -2158,21 +2156,21 @@
       <c r="E37" s="66"/>
     </row>
     <row r="38" spans="1:8" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="170" t="s">
+      <c r="A38" s="162" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="159"/>
+      <c r="B38" s="160"/>
       <c r="C38" s="55"/>
-      <c r="D38" s="186">
+      <c r="D38" s="155">
         <v>87562.7</v>
       </c>
       <c r="E38" s="106"/>
     </row>
     <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="170" t="s">
+      <c r="A39" s="162" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="159"/>
+      <c r="B39" s="160"/>
       <c r="C39" s="55"/>
       <c r="D39" s="153">
         <v>6646.91</v>
@@ -2336,12 +2334,12 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="158" t="s">
+      <c r="A52" s="159" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="159"/>
+      <c r="B52" s="160"/>
       <c r="C52" s="56"/>
-      <c r="D52" s="187">
+      <c r="D52" s="156">
         <v>71000</v>
       </c>
       <c r="E52" s="90" t="s">
@@ -2489,26 +2487,26 @@
       <c r="E67" s="103"/>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="158" t="s">
+      <c r="A68" s="159" t="s">
         <v>161</v>
       </c>
-      <c r="B68" s="160"/>
+      <c r="B68" s="165"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="164">
+      <c r="D68" s="169">
         <v>181000</v>
       </c>
-      <c r="E68" s="166"/>
+      <c r="E68" s="171"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="161"/>
-      <c r="B69" s="162"/>
+      <c r="A69" s="166"/>
+      <c r="B69" s="167"/>
       <c r="C69" s="53"/>
-      <c r="D69" s="165"/>
-      <c r="E69" s="167"/>
+      <c r="D69" s="170"/>
+      <c r="E69" s="172"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="158"/>
-      <c r="B70" s="159"/>
+      <c r="A70" s="159"/>
+      <c r="B70" s="160"/>
       <c r="C70" s="53"/>
       <c r="D70" s="34"/>
       <c r="E70" s="130"/>
@@ -2586,25 +2584,25 @@
     <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="155"/>
-      <c r="B83" s="156"/>
-      <c r="C83" s="156"/>
-      <c r="D83" s="156"/>
-      <c r="E83" s="156"/>
+      <c r="A83" s="163"/>
+      <c r="B83" s="158"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="158"/>
+      <c r="E83" s="158"/>
     </row>
     <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="156"/>
-      <c r="B84" s="156"/>
-      <c r="C84" s="156"/>
-      <c r="D84" s="156"/>
-      <c r="E84" s="156"/>
+      <c r="A84" s="158"/>
+      <c r="B84" s="158"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
     </row>
     <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="156"/>
-      <c r="B85" s="156"/>
-      <c r="C85" s="156"/>
-      <c r="D85" s="156"/>
-      <c r="E85" s="156"/>
+      <c r="A85" s="158"/>
+      <c r="B85" s="158"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
@@ -2764,16 +2762,16 @@
     <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="107" spans="1:4" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="157" t="s">
+      <c r="A108" s="164" t="s">
         <v>58</v>
       </c>
-      <c r="B108" s="156"/>
-      <c r="C108" s="156"/>
+      <c r="B108" s="158"/>
+      <c r="C108" s="158"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="156"/>
-      <c r="B109" s="156"/>
-      <c r="C109" s="156"/>
+      <c r="A109" s="158"/>
+      <c r="B109" s="158"/>
+      <c r="C109" s="158"/>
     </row>
     <row r="110" spans="1:4" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="55"/>
@@ -2801,40 +2799,35 @@
       <c r="M113" s="8"/>
     </row>
     <row r="114" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="163"/>
-      <c r="B114" s="156"/>
-      <c r="C114" s="156"/>
-      <c r="D114" s="156"/>
-      <c r="E114" s="156"/>
+      <c r="A114" s="168"/>
+      <c r="B114" s="158"/>
+      <c r="C114" s="158"/>
+      <c r="D114" s="158"/>
+      <c r="E114" s="158"/>
     </row>
     <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="156"/>
-      <c r="B115" s="156"/>
-      <c r="C115" s="156"/>
-      <c r="D115" s="156"/>
-      <c r="E115" s="156"/>
+      <c r="A115" s="158"/>
+      <c r="B115" s="158"/>
+      <c r="C115" s="158"/>
+      <c r="D115" s="158"/>
+      <c r="E115" s="158"/>
     </row>
     <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="156"/>
-      <c r="B116" s="156"/>
-      <c r="C116" s="156"/>
-      <c r="D116" s="156"/>
-      <c r="E116" s="156"/>
+      <c r="A116" s="158"/>
+      <c r="B116" s="158"/>
+      <c r="C116" s="158"/>
+      <c r="D116" s="158"/>
+      <c r="E116" s="158"/>
     </row>
     <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="156"/>
-      <c r="B117" s="156"/>
-      <c r="C117" s="156"/>
-      <c r="D117" s="156"/>
-      <c r="E117" s="156"/>
+      <c r="A117" s="158"/>
+      <c r="B117" s="158"/>
+      <c r="C117" s="158"/>
+      <c r="D117" s="158"/>
+      <c r="E117" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A83:E85"/>
     <mergeCell ref="A108:C109"/>
     <mergeCell ref="A70:B70"/>
@@ -2842,6 +2835,11 @@
     <mergeCell ref="A114:E117"/>
     <mergeCell ref="D68:D69"/>
     <mergeCell ref="E68:E69"/>
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2883,18 +2881,18 @@
         <v>59</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="183" t="s">
+      <c r="F1" s="177" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="158"/>
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="158"/>
+      <c r="O1" s="158"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2917,11 +2915,11 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="177">
+      <c r="O2" s="182">
         <f>T4</f>
         <v>4000000</v>
       </c>
-      <c r="P2" s="156"/>
+      <c r="P2" s="158"/>
       <c r="Q2" s="15"/>
     </row>
     <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2943,17 +2941,17 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="181">
+      <c r="O3" s="186">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="182"/>
+      <c r="P3" s="187"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="180" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="178" t="s">
+      <c r="B4" s="183" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="173" t="s">
@@ -2962,7 +2960,7 @@
       <c r="D4" s="173" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="174" t="s">
+      <c r="E4" s="175" t="s">
         <v>68</v>
       </c>
       <c r="F4" s="173" t="s">
@@ -2974,28 +2972,28 @@
       <c r="H4" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="174" t="s">
+      <c r="I4" s="175" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="184" t="s">
+      <c r="J4" s="178" t="s">
         <v>73</v>
       </c>
-      <c r="K4" s="176" t="s">
+      <c r="K4" s="181" t="s">
         <v>74</v>
       </c>
-      <c r="L4" s="185" t="s">
+      <c r="L4" s="179" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="176" t="s">
+      <c r="M4" s="181" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="176" t="s">
+      <c r="N4" s="181" t="s">
         <v>77</v>
       </c>
       <c r="O4" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="180" t="s">
+      <c r="P4" s="185" t="s">
         <v>79</v>
       </c>
       <c r="S4" s="43"/>
@@ -3004,25 +3002,25 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="172"/>
-      <c r="B5" s="179"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="172"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
-      <c r="L5" s="172"/>
-      <c r="M5" s="175"/>
-      <c r="N5" s="175"/>
+      <c r="A5" s="174"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="174"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="176"/>
+      <c r="J5" s="176"/>
+      <c r="K5" s="176"/>
+      <c r="L5" s="174"/>
+      <c r="M5" s="176"/>
+      <c r="N5" s="176"/>
       <c r="O5" s="59" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/10</v>
       </c>
-      <c r="P5" s="172"/>
+      <c r="P5" s="174"/>
       <c r="T5" t="s">
         <v>163</v>
       </c>
@@ -4213,90 +4211,90 @@
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="163" t="s">
+      <c r="D28" s="168" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="156"/>
-      <c r="F28" s="156"/>
-      <c r="G28" s="156"/>
-      <c r="H28" s="156"/>
-      <c r="I28" s="156"/>
-      <c r="J28" s="156"/>
-      <c r="K28" s="156"/>
-      <c r="L28" s="156"/>
-      <c r="M28" s="156"/>
-      <c r="N28" s="156"/>
-      <c r="O28" s="156"/>
+      <c r="E28" s="158"/>
+      <c r="F28" s="158"/>
+      <c r="G28" s="158"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="158"/>
+      <c r="J28" s="158"/>
+      <c r="K28" s="158"/>
+      <c r="L28" s="158"/>
+      <c r="M28" s="158"/>
+      <c r="N28" s="158"/>
+      <c r="O28" s="158"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="156"/>
-      <c r="G29" s="156"/>
-      <c r="H29" s="156"/>
-      <c r="I29" s="156"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="156"/>
-      <c r="L29" s="156"/>
-      <c r="M29" s="156"/>
-      <c r="N29" s="156"/>
-      <c r="O29" s="156"/>
+      <c r="D29" s="158"/>
+      <c r="E29" s="158"/>
+      <c r="F29" s="158"/>
+      <c r="G29" s="158"/>
+      <c r="H29" s="158"/>
+      <c r="I29" s="158"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="158"/>
+      <c r="L29" s="158"/>
+      <c r="M29" s="158"/>
+      <c r="N29" s="158"/>
+      <c r="O29" s="158"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="156"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="156"/>
-      <c r="G30" s="156"/>
-      <c r="H30" s="156"/>
-      <c r="I30" s="156"/>
-      <c r="J30" s="156"/>
-      <c r="K30" s="156"/>
-      <c r="L30" s="156"/>
-      <c r="M30" s="156"/>
-      <c r="N30" s="156"/>
-      <c r="O30" s="156"/>
+      <c r="D30" s="158"/>
+      <c r="E30" s="158"/>
+      <c r="F30" s="158"/>
+      <c r="G30" s="158"/>
+      <c r="H30" s="158"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
+      <c r="L30" s="158"/>
+      <c r="M30" s="158"/>
+      <c r="N30" s="158"/>
+      <c r="O30" s="158"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="156"/>
-      <c r="L31" s="156"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="156"/>
-      <c r="O31" s="156"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="158"/>
+      <c r="G31" s="158"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="158"/>
+      <c r="O31" s="158"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="156"/>
-      <c r="I32" s="156"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="156"/>
-      <c r="M32" s="156"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="156"/>
+      <c r="D32" s="158"/>
+      <c r="E32" s="158"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="158"/>
+      <c r="H32" s="158"/>
+      <c r="I32" s="158"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="158"/>
+      <c r="M32" s="158"/>
+      <c r="N32" s="158"/>
+      <c r="O32" s="158"/>
     </row>
     <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="156"/>
-      <c r="I33" s="156"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="156"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="156"/>
+      <c r="D33" s="158"/>
+      <c r="E33" s="158"/>
+      <c r="F33" s="158"/>
+      <c r="G33" s="158"/>
+      <c r="H33" s="158"/>
+      <c r="I33" s="158"/>
+      <c r="J33" s="158"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="158"/>
+      <c r="M33" s="158"/>
+      <c r="N33" s="158"/>
+      <c r="O33" s="158"/>
       <c r="R33" s="104"/>
       <c r="S33" s="104"/>
       <c r="T33" s="104"/>
@@ -4304,13 +4302,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4323,6 +4314,13 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
